--- a/RmFishing/translations.xlsx
+++ b/RmFishing/translations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProgramingTempPlace\Elin\ElinMod_rai\RmFishing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B557BF44-8BF9-4492-B97B-DCBB70BB5308}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA0AFB9-3FA6-41C0-9F7D-B4CE17F7F989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -52,16 +52,6 @@
   </si>
   <si>
     <t>RmFishing (CN)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>釣りのコストを変更する</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンコウ</t>
-    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -143,6 +133,16 @@
   </si>
   <si>
     <t>mod.tooltip</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>釣りのコストを変更する TEST</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -200,20 +200,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -349,480 +347,471 @@
   <dimension ref="A1:D100"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="66" style="4" customWidth="1"/>
-    <col min="3" max="3" width="65.7109375" style="4" customWidth="1"/>
-    <col min="4" max="4" width="67.7109375" style="4" customWidth="1"/>
-    <col min="5" max="16384" width="11.5703125" style="1"/>
+    <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="66" style="2" customWidth="1"/>
+    <col min="3" max="3" width="65.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="67.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
     <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-    </row>
-    <row r="16" spans="1:4" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-    </row>
-    <row r="18" spans="1:4" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-    </row>
-    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-    </row>
-    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-    </row>
-    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-    </row>
-    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-    </row>
-    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-    </row>
-    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-    </row>
-    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-    </row>
-    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-    </row>
-    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-    </row>
-    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+    </row>
+    <row r="26" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+    </row>
+    <row r="27" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+    </row>
+    <row r="28" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+    </row>
+    <row r="29" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+    </row>
+    <row r="30" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+    </row>
+    <row r="32" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
     </row>
     <row r="39" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
     </row>
     <row r="43" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
     </row>
     <row r="45" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
     </row>
     <row r="47" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
     </row>
     <row r="48" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
     </row>
     <row r="50" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
     </row>
     <row r="56" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="3:4" ht="62.65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
     </row>
     <row r="61" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
     </row>
     <row r="62" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
     </row>
     <row r="63" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
     </row>
     <row r="64" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
     </row>
     <row r="65" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
     </row>
     <row r="66" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C66" s="6"/>
-      <c r="D66" s="7"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="5"/>
     </row>
     <row r="67" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C67" s="5"/>
-      <c r="D67" s="6"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="4"/>
     </row>
     <row r="68" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C68" s="5"/>
-      <c r="D68" s="6"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="4"/>
     </row>
     <row r="69" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C69" s="5"/>
-      <c r="D69" s="6"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="4"/>
     </row>
     <row r="70" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C70" s="5"/>
-      <c r="D70" s="6"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="4"/>
     </row>
     <row r="71" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C71" s="5"/>
-      <c r="D71" s="6"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="4"/>
     </row>
     <row r="72" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C72" s="5"/>
-      <c r="D72" s="6"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="4"/>
     </row>
     <row r="73" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C73" s="5"/>
-      <c r="D73" s="6"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="4"/>
     </row>
     <row r="74" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C74" s="5"/>
-      <c r="D74" s="6"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
     </row>
     <row r="75" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C75" s="5"/>
-      <c r="D75" s="6"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="4"/>
     </row>
     <row r="76" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C76" s="5"/>
-      <c r="D76" s="6"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="4"/>
     </row>
     <row r="77" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C77" s="5"/>
-      <c r="D77" s="6"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="4"/>
     </row>
     <row r="78" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C78" s="5"/>
-      <c r="D78" s="6"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="4"/>
     </row>
     <row r="79" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C79" s="5"/>
-      <c r="D79" s="6"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="4"/>
     </row>
     <row r="80" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C80" s="5"/>
-      <c r="D80" s="6"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="4"/>
     </row>
     <row r="81" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C81" s="5"/>
-      <c r="D81" s="6"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4"/>
     </row>
     <row r="82" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C82" s="5"/>
-      <c r="D82" s="6"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="4"/>
     </row>
     <row r="83" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C83" s="5"/>
-      <c r="D83" s="6"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="4"/>
     </row>
     <row r="84" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C84" s="5"/>
-      <c r="D84" s="6"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="4"/>
     </row>
     <row r="85" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C85" s="5"/>
-      <c r="D85" s="6"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="4"/>
     </row>
     <row r="86" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C86" s="5"/>
-      <c r="D86" s="6"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
     </row>
     <row r="87" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C87" s="5"/>
-      <c r="D87" s="6"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="4"/>
     </row>
     <row r="88" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C88" s="5"/>
-      <c r="D88" s="6"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="4"/>
     </row>
     <row r="89" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C89" s="5"/>
-      <c r="D89" s="6"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="4"/>
     </row>
     <row r="90" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C90" s="5"/>
-      <c r="D90" s="6"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4"/>
     </row>
     <row r="91" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C91" s="5"/>
-      <c r="D91" s="6"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="4"/>
     </row>
     <row r="92" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C92" s="5"/>
-      <c r="D92" s="6"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="4"/>
     </row>
     <row r="93" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C93" s="5"/>
-      <c r="D93" s="6"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="4"/>
     </row>
     <row r="94" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C94" s="5"/>
-      <c r="D94" s="6"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4"/>
     </row>
     <row r="95" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C95" s="5"/>
-      <c r="D95" s="6"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="4"/>
     </row>
     <row r="96" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C96" s="5"/>
-      <c r="D96" s="6"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="4"/>
     </row>
     <row r="97" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C97" s="5"/>
-      <c r="D97" s="6"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="4"/>
     </row>
     <row r="98" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C98" s="5"/>
-      <c r="D98" s="6"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="4"/>
     </row>
     <row r="99" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C99" s="5"/>
-      <c r="D99" s="6"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="4"/>
     </row>
     <row r="100" spans="3:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C100" s="5"/>
-      <c r="D100" s="6"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4"/>

--- a/RmFishing/translations.xlsx
+++ b/RmFishing/translations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProgramingTempPlace\Elin\ElinMod_rai\RmFishing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA0AFB9-3FA6-41C0-9F7D-B4CE17F7F989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F0EBD7-E4F7-407B-AE5F-1D4CB0307573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,14 +43,6 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>RmFishing (EN)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>RmFishing (JP)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
     <t>RmFishing (CN)</t>
     <phoneticPr fontId="4"/>
   </si>
@@ -136,13 +128,21 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>釣りのコストを変更する TEST</t>
+    <t>釣りのコストを変更する TEST TTT</t>
     <rPh sb="0" eb="1">
       <t>ツ</t>
     </rPh>
     <rPh sb="7" eb="9">
       <t>ヘンコウ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>RmFishing (EN) a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>RmFishing (JP)b</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -372,69 +372,69 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">

--- a/RmFishing/translations.xlsx
+++ b/RmFishing/translations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProgramingTempPlace\Elin\ElinMod_rai\RmFishing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F0EBD7-E4F7-407B-AE5F-1D4CB0307573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47FA60E-FFE6-44CA-84F9-00F85E189E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,21 +128,21 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>釣りのコストを変更する TEST TTT</t>
+    <t>RmFishing (EN) a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>RmFishing (JP)b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>釣りのコストを変更する TEST TTTS</t>
     <rPh sb="0" eb="1">
       <t>ツ</t>
     </rPh>
     <rPh sb="7" eb="9">
       <t>ヘンコウ</t>
     </rPh>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>RmFishing (EN) a</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>RmFishing (JP)b</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -372,10 +372,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -389,7 +389,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>12</v>

--- a/RmFishing/translations.xlsx
+++ b/RmFishing/translations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ProgramingTempPlace\Elin\ElinMod_rai\RmFishing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D47FA60E-FFE6-44CA-84F9-00F85E189E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713DB955-97E8-403F-BDD2-AEF7E5943913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38505" yWindow="345" windowWidth="28800" windowHeight="15885" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>id</t>
   </si>
@@ -57,92 +57,138 @@
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>消費コストを「スタミナ」と「釣り餌」を逆にする（スタミナ消費がとなる）</t>
+    <t>Set both consumption costs to “1”.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>两个消耗成本都设为 “1”。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>改变捕鱼成本（自动、机器翻译）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Change the cost of fishing(automatic, machine translation)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>デフォルトコスト</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Defoult Cost.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>fishingCost01</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>fishingCost02</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>fishingCost03</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>默认成本</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>mod.tooltip</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t xml:space="preserve">RmFishing (EN) </t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>RmFishing (JP)</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>釣りのコストを変更する</t>
+    <rPh sb="0" eb="1">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>fishingCost04</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Set “stamina”  costs to “1”.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>消費コストを「スタミナ」のみ「1」にする</t>
     <rPh sb="0" eb="2">
       <t>ショウヒ</t>
     </rPh>
-    <rPh sb="14" eb="15">
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>仅将“体力”的消耗成本设置为“1”。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>fishingCost05</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Set  “fishing bait”  costs to “1”.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>消費コストを「釣り餌」のみ「1」にする</t>
+    <rPh sb="0" eb="2">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
       <t>ツ</t>
     </rPh>
-    <rPh sb="16" eb="17">
+    <rPh sb="9" eb="10">
+      <t>エサ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>仅将“鱼饵”的消耗成本设置为“1”。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>(Repeal) Reverse “stamina” and “fishing bait” consumption costs (stamina consumption becomes)</t>
+  </si>
+  <si>
+    <t>（廃止）消費コストを「スタミナ」と「釣り餌」を逆にする（スタミナ消費がとなる）</t>
+    <rPh sb="1" eb="3">
+      <t>ハイシ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショウヒ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>ツ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
       <t>エ</t>
     </rPh>
-    <rPh sb="19" eb="20">
+    <rPh sb="23" eb="24">
       <t>ギャク</t>
     </rPh>
-    <rPh sb="28" eb="30">
+    <rPh sb="32" eb="34">
       <t>ショウヒ</t>
     </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
-    <t>Reverse “stamina” and “fishing bait” consumption costs (stamina consumption becomes)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>Set both consumption costs to “1”.</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>两个消耗成本都设为 “1”。</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>反转 “体力 ”和 “鱼饵 ”消耗成本（体力消耗变为）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>改变捕鱼成本（自动、机器翻译）</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>Change the cost of fishing(automatic, machine translation)</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>デフォルトコスト</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>Defoult Cost.</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>fishingCost01</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>fishingCost02</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>fishingCost03</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>默认成本</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>mod.tooltip</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>RmFishing (EN) a</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>RmFishing (JP)b</t>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <t>釣りのコストを変更する TEST TTTS</t>
-    <rPh sb="0" eb="1">
-      <t>ツ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ヘンコウ</t>
-    </rPh>
+    <t>（废除）反转 “体力 ”和 “鱼饵 ”消耗成本（体力消耗变为）</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -372,10 +418,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -383,67 +429,87 @@
     </row>
     <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="33" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.2">
       <c r="C9" s="3"/>
